--- a/Data/EC/NIT-9007517788.xlsx
+++ b/Data/EC/NIT-9007517788.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Documents\NIYARAKY\MACROS AJUSTADAS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ysarm\OneDrive\Desktop\MACROS\2- MACRO COMFENALCO CARTAGENA ACTUALIZACION\Estados De Cuenta\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B93CB74E-5F58-436F-B936-D4C6863FF35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{1F5F1ED6-FF5F-467F-908E-41638C7B542A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{C7242EE8-DE26-4793-84B6-96A967154A3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{D170DCC5-F417-46CA-B3D5-1C994AAF7499}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="336" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="340" uniqueCount="103">
   <si>
     <t>Tipo Doc Trabajador</t>
   </si>
@@ -71,241 +71,247 @@
     <t>PLINIO HERNANDEZ CANTILLO</t>
   </si>
   <si>
+    <t>2301</t>
+  </si>
+  <si>
+    <t>2212</t>
+  </si>
+  <si>
+    <t>2211</t>
+  </si>
+  <si>
+    <t>2210</t>
+  </si>
+  <si>
+    <t>2209</t>
+  </si>
+  <si>
+    <t>2208</t>
+  </si>
+  <si>
+    <t>2207</t>
+  </si>
+  <si>
+    <t>2206</t>
+  </si>
+  <si>
+    <t>2205</t>
+  </si>
+  <si>
+    <t>2204</t>
+  </si>
+  <si>
+    <t>2203</t>
+  </si>
+  <si>
+    <t>2202</t>
+  </si>
+  <si>
+    <t>2201</t>
+  </si>
+  <si>
+    <t>2112</t>
+  </si>
+  <si>
+    <t>2111</t>
+  </si>
+  <si>
+    <t>2110</t>
+  </si>
+  <si>
+    <t>2109</t>
+  </si>
+  <si>
+    <t>2108</t>
+  </si>
+  <si>
+    <t>2107</t>
+  </si>
+  <si>
+    <t>2106</t>
+  </si>
+  <si>
+    <t>2105</t>
+  </si>
+  <si>
+    <t>2104</t>
+  </si>
+  <si>
+    <t>2103</t>
+  </si>
+  <si>
+    <t>2102</t>
+  </si>
+  <si>
+    <t>2101</t>
+  </si>
+  <si>
+    <t>2012</t>
+  </si>
+  <si>
+    <t>2011</t>
+  </si>
+  <si>
+    <t>2010</t>
+  </si>
+  <si>
+    <t>2009</t>
+  </si>
+  <si>
+    <t>2008</t>
+  </si>
+  <si>
+    <t>2007</t>
+  </si>
+  <si>
+    <t>2006</t>
+  </si>
+  <si>
+    <t>2005</t>
+  </si>
+  <si>
+    <t>2004</t>
+  </si>
+  <si>
+    <t>2003</t>
+  </si>
+  <si>
+    <t>2002</t>
+  </si>
+  <si>
+    <t>2001</t>
+  </si>
+  <si>
+    <t>1912</t>
+  </si>
+  <si>
+    <t>1911</t>
+  </si>
+  <si>
+    <t>1910</t>
+  </si>
+  <si>
+    <t>1909</t>
+  </si>
+  <si>
+    <t>1908</t>
+  </si>
+  <si>
+    <t>1907</t>
+  </si>
+  <si>
+    <t>1906</t>
+  </si>
+  <si>
+    <t>1905</t>
+  </si>
+  <si>
+    <t>1904</t>
+  </si>
+  <si>
+    <t>1903</t>
+  </si>
+  <si>
+    <t>1902</t>
+  </si>
+  <si>
+    <t>1901</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>1712</t>
+  </si>
+  <si>
+    <t>1711</t>
+  </si>
+  <si>
+    <t>1710</t>
+  </si>
+  <si>
+    <t>1709</t>
+  </si>
+  <si>
+    <t>1708</t>
+  </si>
+  <si>
+    <t>1707</t>
+  </si>
+  <si>
+    <t>1706</t>
+  </si>
+  <si>
+    <t>1705</t>
+  </si>
+  <si>
+    <t>1704</t>
+  </si>
+  <si>
+    <t>1703</t>
+  </si>
+  <si>
+    <t>1702</t>
+  </si>
+  <si>
+    <t>1701</t>
+  </si>
+  <si>
+    <t>1612</t>
+  </si>
+  <si>
+    <t>1611</t>
+  </si>
+  <si>
+    <t>1610</t>
+  </si>
+  <si>
+    <t>1609</t>
+  </si>
+  <si>
+    <t>1608</t>
+  </si>
+  <si>
     <t>1607</t>
   </si>
   <si>
-    <t>1608</t>
-  </si>
-  <si>
-    <t>1609</t>
-  </si>
-  <si>
-    <t>1610</t>
-  </si>
-  <si>
-    <t>1611</t>
-  </si>
-  <si>
-    <t>1612</t>
-  </si>
-  <si>
-    <t>1701</t>
-  </si>
-  <si>
-    <t>1702</t>
-  </si>
-  <si>
-    <t>1703</t>
-  </si>
-  <si>
-    <t>1704</t>
-  </si>
-  <si>
-    <t>1705</t>
-  </si>
-  <si>
-    <t>1706</t>
-  </si>
-  <si>
-    <t>1707</t>
-  </si>
-  <si>
-    <t>1708</t>
-  </si>
-  <si>
-    <t>1709</t>
-  </si>
-  <si>
-    <t>1710</t>
-  </si>
-  <si>
-    <t>1711</t>
-  </si>
-  <si>
-    <t>1712</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>1901</t>
-  </si>
-  <si>
-    <t>1902</t>
-  </si>
-  <si>
-    <t>1903</t>
-  </si>
-  <si>
-    <t>1904</t>
-  </si>
-  <si>
-    <t>1905</t>
-  </si>
-  <si>
-    <t>1906</t>
-  </si>
-  <si>
-    <t>1907</t>
-  </si>
-  <si>
-    <t>1908</t>
-  </si>
-  <si>
-    <t>1909</t>
-  </si>
-  <si>
-    <t>1910</t>
-  </si>
-  <si>
-    <t>1911</t>
-  </si>
-  <si>
-    <t>1912</t>
-  </si>
-  <si>
-    <t>2001</t>
-  </si>
-  <si>
-    <t>2002</t>
-  </si>
-  <si>
-    <t>2003</t>
-  </si>
-  <si>
-    <t>2004</t>
-  </si>
-  <si>
-    <t>2005</t>
-  </si>
-  <si>
-    <t>2006</t>
-  </si>
-  <si>
-    <t>2007</t>
-  </si>
-  <si>
-    <t>2008</t>
-  </si>
-  <si>
-    <t>2009</t>
-  </si>
-  <si>
-    <t>2010</t>
-  </si>
-  <si>
-    <t>2011</t>
-  </si>
-  <si>
-    <t>2012</t>
-  </si>
-  <si>
-    <t>2101</t>
-  </si>
-  <si>
-    <t>2102</t>
-  </si>
-  <si>
-    <t>2103</t>
-  </si>
-  <si>
-    <t>2104</t>
-  </si>
-  <si>
-    <t>2105</t>
-  </si>
-  <si>
-    <t>2106</t>
-  </si>
-  <si>
-    <t>2107</t>
-  </si>
-  <si>
-    <t>2108</t>
-  </si>
-  <si>
-    <t>2109</t>
-  </si>
-  <si>
-    <t>2110</t>
-  </si>
-  <si>
-    <t>2111</t>
-  </si>
-  <si>
-    <t>2112</t>
-  </si>
-  <si>
-    <t>2201</t>
-  </si>
-  <si>
-    <t>2202</t>
-  </si>
-  <si>
-    <t>2203</t>
-  </si>
-  <si>
-    <t>2204</t>
-  </si>
-  <si>
-    <t>2205</t>
-  </si>
-  <si>
-    <t>2206</t>
-  </si>
-  <si>
-    <t>2207</t>
-  </si>
-  <si>
-    <t>2208</t>
-  </si>
-  <si>
-    <t>2209</t>
-  </si>
-  <si>
-    <t>2210</t>
-  </si>
-  <si>
-    <t>2211</t>
-  </si>
-  <si>
-    <t>2212</t>
-  </si>
-  <si>
-    <t>2301</t>
+    <t>73475824</t>
+  </si>
+  <si>
+    <t>ANIBAL MENDOZA CHAMORRO</t>
   </si>
   <si>
     <t>ESTADO DE CUENTA</t>
@@ -404,9 +410,7 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
+      <right/>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -419,7 +423,9 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
       <top style="thin">
         <color indexed="64"/>
       </top>
@@ -619,23 +625,23 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="3" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -663,10 +669,10 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="10" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -704,22 +710,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>667900</xdr:colOff>
+      <xdr:colOff>717113</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>62300</xdr:rowOff>
+      <xdr:rowOff>75000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
-      <xdr:colOff>430650</xdr:colOff>
+      <xdr:colOff>435413</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>121850</xdr:rowOff>
+      <xdr:rowOff>115500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF9C8E1E-906E-5FC7-018A-2CC8C84CE97D}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03F2EDCF-599B-1814-2450-114E400E266D}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -741,7 +747,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="921900" y="246450"/>
+          <a:off x="964763" y="265500"/>
           <a:ext cx="975600" cy="612000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1070,27 +1076,27 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1101300-C4CC-444E-84EE-B567DA3A110F}">
-  <dimension ref="B2:J100"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC648014-88AB-42DB-8417-E50642246695}">
+  <dimension ref="B2:J101"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="3.6328125" customWidth="1"/>
-    <col min="2" max="2" width="18.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.7265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="27.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.1796875" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.36328125" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="19.36328125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="18.08984375" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="15" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="3.7109375" customWidth="1"/>
+    <col min="2" max="2" width="19.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.7109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="29.140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="15.28515625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B2" s="3"/>
       <c r="C2" s="28"/>
       <c r="D2" s="29" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E2" s="29"/>
       <c r="F2" s="29"/>
@@ -1099,7 +1105,7 @@
       <c r="I2" s="29"/>
       <c r="J2" s="29"/>
     </row>
-    <row r="3" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="3" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B3" s="3"/>
       <c r="C3" s="28"/>
       <c r="D3" s="30"/>
@@ -1110,7 +1116,7 @@
       <c r="I3" s="30"/>
       <c r="J3" s="30"/>
     </row>
-    <row r="4" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="4" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B4" s="3"/>
       <c r="C4" s="28"/>
       <c r="D4" s="30"/>
@@ -1121,7 +1127,7 @@
       <c r="I4" s="30"/>
       <c r="J4" s="30"/>
     </row>
-    <row r="5" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="5" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B5" s="3"/>
       <c r="C5" s="28"/>
       <c r="D5" s="31"/>
@@ -1132,10 +1138,10 @@
       <c r="I5" s="31"/>
       <c r="J5" s="31"/>
     </row>
-    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="7" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="7" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B7" s="4" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C7" s="4"/>
       <c r="D7" s="27"/>
@@ -1148,8 +1154,8 @@
       <c r="I7" s="6"/>
       <c r="J7" s="6"/>
     </row>
-    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="9" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="9" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B9" s="4" t="s">
         <v>6</v>
       </c>
@@ -1164,15 +1170,15 @@
       <c r="I9" s="6"/>
       <c r="J9" s="6"/>
     </row>
-    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="11" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="2:10" ht="6.75" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="11" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B11" s="4" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C11" s="4"/>
       <c r="D11" s="27"/>
       <c r="E11" s="7">
-        <v>2368017</v>
+        <v>2397617</v>
       </c>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
@@ -1180,17 +1186,17 @@
       <c r="I11" s="7"/>
       <c r="J11" s="7"/>
     </row>
-    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.35"/>
-    <row r="13" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="2:10" ht="4.5" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="13" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B13" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C13" s="5">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D13" s="5"/>
       <c r="E13" s="8" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="F13" s="5">
         <v>79</v>
@@ -1200,7 +1206,7 @@
       <c r="I13" s="5"/>
       <c r="J13" s="5"/>
     </row>
-    <row r="15" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B15" s="10" t="s">
         <v>0</v>
       </c>
@@ -1220,16 +1226,16 @@
         <v>5</v>
       </c>
       <c r="H15" s="13" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="I15" s="13" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J15" s="14" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="16" spans="2:10" x14ac:dyDescent="0.35">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="16" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B16" s="15" t="s">
         <v>8</v>
       </c>
@@ -1243,7 +1249,7 @@
         <v>11</v>
       </c>
       <c r="F16" s="18">
-        <v>27578</v>
+        <v>26041</v>
       </c>
       <c r="G16" s="18">
         <v>781242</v>
@@ -1252,7 +1258,7 @@
       <c r="I16" s="19"/>
       <c r="J16" s="20"/>
     </row>
-    <row r="17" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B17" s="15" t="s">
         <v>8</v>
       </c>
@@ -1266,7 +1272,7 @@
         <v>12</v>
       </c>
       <c r="F17" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G17" s="18">
         <v>781242</v>
@@ -1275,7 +1281,7 @@
       <c r="I17" s="19"/>
       <c r="J17" s="20"/>
     </row>
-    <row r="18" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B18" s="15" t="s">
         <v>8</v>
       </c>
@@ -1289,7 +1295,7 @@
         <v>13</v>
       </c>
       <c r="F18" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G18" s="18">
         <v>781242</v>
@@ -1298,7 +1304,7 @@
       <c r="I18" s="19"/>
       <c r="J18" s="20"/>
     </row>
-    <row r="19" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B19" s="15" t="s">
         <v>8</v>
       </c>
@@ -1312,7 +1318,7 @@
         <v>14</v>
       </c>
       <c r="F19" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G19" s="18">
         <v>781242</v>
@@ -1321,7 +1327,7 @@
       <c r="I19" s="19"/>
       <c r="J19" s="20"/>
     </row>
-    <row r="20" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B20" s="15" t="s">
         <v>8</v>
       </c>
@@ -1335,7 +1341,7 @@
         <v>15</v>
       </c>
       <c r="F20" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G20" s="18">
         <v>781242</v>
@@ -1344,7 +1350,7 @@
       <c r="I20" s="19"/>
       <c r="J20" s="20"/>
     </row>
-    <row r="21" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B21" s="15" t="s">
         <v>8</v>
       </c>
@@ -1358,7 +1364,7 @@
         <v>16</v>
       </c>
       <c r="F21" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G21" s="18">
         <v>781242</v>
@@ -1367,7 +1373,7 @@
       <c r="I21" s="19"/>
       <c r="J21" s="20"/>
     </row>
-    <row r="22" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B22" s="15" t="s">
         <v>8</v>
       </c>
@@ -1381,7 +1387,7 @@
         <v>17</v>
       </c>
       <c r="F22" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G22" s="18">
         <v>781242</v>
@@ -1390,7 +1396,7 @@
       <c r="I22" s="19"/>
       <c r="J22" s="20"/>
     </row>
-    <row r="23" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B23" s="15" t="s">
         <v>8</v>
       </c>
@@ -1404,7 +1410,7 @@
         <v>18</v>
       </c>
       <c r="F23" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G23" s="18">
         <v>781242</v>
@@ -1413,7 +1419,7 @@
       <c r="I23" s="19"/>
       <c r="J23" s="20"/>
     </row>
-    <row r="24" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B24" s="15" t="s">
         <v>8</v>
       </c>
@@ -1427,7 +1433,7 @@
         <v>19</v>
       </c>
       <c r="F24" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G24" s="18">
         <v>781242</v>
@@ -1436,7 +1442,7 @@
       <c r="I24" s="19"/>
       <c r="J24" s="20"/>
     </row>
-    <row r="25" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B25" s="15" t="s">
         <v>8</v>
       </c>
@@ -1450,7 +1456,7 @@
         <v>20</v>
       </c>
       <c r="F25" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G25" s="18">
         <v>781242</v>
@@ -1459,7 +1465,7 @@
       <c r="I25" s="19"/>
       <c r="J25" s="20"/>
     </row>
-    <row r="26" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B26" s="15" t="s">
         <v>8</v>
       </c>
@@ -1473,7 +1479,7 @@
         <v>21</v>
       </c>
       <c r="F26" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G26" s="18">
         <v>781242</v>
@@ -1482,7 +1488,7 @@
       <c r="I26" s="19"/>
       <c r="J26" s="20"/>
     </row>
-    <row r="27" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B27" s="15" t="s">
         <v>8</v>
       </c>
@@ -1496,7 +1502,7 @@
         <v>22</v>
       </c>
       <c r="F27" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G27" s="18">
         <v>781242</v>
@@ -1505,7 +1511,7 @@
       <c r="I27" s="19"/>
       <c r="J27" s="20"/>
     </row>
-    <row r="28" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B28" s="15" t="s">
         <v>8</v>
       </c>
@@ -1519,7 +1525,7 @@
         <v>23</v>
       </c>
       <c r="F28" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G28" s="18">
         <v>781242</v>
@@ -1528,7 +1534,7 @@
       <c r="I28" s="19"/>
       <c r="J28" s="20"/>
     </row>
-    <row r="29" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B29" s="15" t="s">
         <v>8</v>
       </c>
@@ -1542,7 +1548,7 @@
         <v>24</v>
       </c>
       <c r="F29" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G29" s="18">
         <v>781242</v>
@@ -1551,7 +1557,7 @@
       <c r="I29" s="19"/>
       <c r="J29" s="20"/>
     </row>
-    <row r="30" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B30" s="15" t="s">
         <v>8</v>
       </c>
@@ -1565,7 +1571,7 @@
         <v>25</v>
       </c>
       <c r="F30" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G30" s="18">
         <v>781242</v>
@@ -1574,7 +1580,7 @@
       <c r="I30" s="19"/>
       <c r="J30" s="20"/>
     </row>
-    <row r="31" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B31" s="15" t="s">
         <v>8</v>
       </c>
@@ -1588,7 +1594,7 @@
         <v>26</v>
       </c>
       <c r="F31" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G31" s="18">
         <v>781242</v>
@@ -1597,7 +1603,7 @@
       <c r="I31" s="19"/>
       <c r="J31" s="20"/>
     </row>
-    <row r="32" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B32" s="15" t="s">
         <v>8</v>
       </c>
@@ -1611,7 +1617,7 @@
         <v>27</v>
       </c>
       <c r="F32" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G32" s="18">
         <v>781242</v>
@@ -1620,7 +1626,7 @@
       <c r="I32" s="19"/>
       <c r="J32" s="20"/>
     </row>
-    <row r="33" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B33" s="15" t="s">
         <v>8</v>
       </c>
@@ -1634,7 +1640,7 @@
         <v>28</v>
       </c>
       <c r="F33" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G33" s="18">
         <v>781242</v>
@@ -1643,7 +1649,7 @@
       <c r="I33" s="19"/>
       <c r="J33" s="20"/>
     </row>
-    <row r="34" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B34" s="15" t="s">
         <v>8</v>
       </c>
@@ -1657,7 +1663,7 @@
         <v>29</v>
       </c>
       <c r="F34" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G34" s="18">
         <v>781242</v>
@@ -1666,7 +1672,7 @@
       <c r="I34" s="19"/>
       <c r="J34" s="20"/>
     </row>
-    <row r="35" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B35" s="15" t="s">
         <v>8</v>
       </c>
@@ -1680,7 +1686,7 @@
         <v>30</v>
       </c>
       <c r="F35" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G35" s="18">
         <v>781242</v>
@@ -1689,7 +1695,7 @@
       <c r="I35" s="19"/>
       <c r="J35" s="20"/>
     </row>
-    <row r="36" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B36" s="15" t="s">
         <v>8</v>
       </c>
@@ -1703,7 +1709,7 @@
         <v>31</v>
       </c>
       <c r="F36" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G36" s="18">
         <v>781242</v>
@@ -1712,7 +1718,7 @@
       <c r="I36" s="19"/>
       <c r="J36" s="20"/>
     </row>
-    <row r="37" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B37" s="15" t="s">
         <v>8</v>
       </c>
@@ -1726,7 +1732,7 @@
         <v>32</v>
       </c>
       <c r="F37" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G37" s="18">
         <v>781242</v>
@@ -1735,7 +1741,7 @@
       <c r="I37" s="19"/>
       <c r="J37" s="20"/>
     </row>
-    <row r="38" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B38" s="15" t="s">
         <v>8</v>
       </c>
@@ -1749,7 +1755,7 @@
         <v>33</v>
       </c>
       <c r="F38" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G38" s="18">
         <v>781242</v>
@@ -1758,7 +1764,7 @@
       <c r="I38" s="19"/>
       <c r="J38" s="20"/>
     </row>
-    <row r="39" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B39" s="15" t="s">
         <v>8</v>
       </c>
@@ -1772,7 +1778,7 @@
         <v>34</v>
       </c>
       <c r="F39" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G39" s="18">
         <v>781242</v>
@@ -1781,7 +1787,7 @@
       <c r="I39" s="19"/>
       <c r="J39" s="20"/>
     </row>
-    <row r="40" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B40" s="15" t="s">
         <v>8</v>
       </c>
@@ -1795,7 +1801,7 @@
         <v>35</v>
       </c>
       <c r="F40" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G40" s="18">
         <v>781242</v>
@@ -1804,7 +1810,7 @@
       <c r="I40" s="19"/>
       <c r="J40" s="20"/>
     </row>
-    <row r="41" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B41" s="15" t="s">
         <v>8</v>
       </c>
@@ -1818,7 +1824,7 @@
         <v>36</v>
       </c>
       <c r="F41" s="18">
-        <v>27578</v>
+        <v>31249</v>
       </c>
       <c r="G41" s="18">
         <v>781242</v>
@@ -1827,7 +1833,7 @@
       <c r="I41" s="19"/>
       <c r="J41" s="20"/>
     </row>
-    <row r="42" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B42" s="15" t="s">
         <v>8</v>
       </c>
@@ -1850,7 +1856,7 @@
       <c r="I42" s="19"/>
       <c r="J42" s="20"/>
     </row>
-    <row r="43" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B43" s="15" t="s">
         <v>8</v>
       </c>
@@ -1873,7 +1879,7 @@
       <c r="I43" s="19"/>
       <c r="J43" s="20"/>
     </row>
-    <row r="44" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B44" s="15" t="s">
         <v>8</v>
       </c>
@@ -1896,7 +1902,7 @@
       <c r="I44" s="19"/>
       <c r="J44" s="20"/>
     </row>
-    <row r="45" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B45" s="15" t="s">
         <v>8</v>
       </c>
@@ -1919,7 +1925,7 @@
       <c r="I45" s="19"/>
       <c r="J45" s="20"/>
     </row>
-    <row r="46" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B46" s="15" t="s">
         <v>8</v>
       </c>
@@ -1942,7 +1948,7 @@
       <c r="I46" s="19"/>
       <c r="J46" s="20"/>
     </row>
-    <row r="47" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B47" s="15" t="s">
         <v>8</v>
       </c>
@@ -1965,7 +1971,7 @@
       <c r="I47" s="19"/>
       <c r="J47" s="20"/>
     </row>
-    <row r="48" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B48" s="15" t="s">
         <v>8</v>
       </c>
@@ -1988,7 +1994,7 @@
       <c r="I48" s="19"/>
       <c r="J48" s="20"/>
     </row>
-    <row r="49" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B49" s="15" t="s">
         <v>8</v>
       </c>
@@ -2011,7 +2017,7 @@
       <c r="I49" s="19"/>
       <c r="J49" s="20"/>
     </row>
-    <row r="50" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B50" s="15" t="s">
         <v>8</v>
       </c>
@@ -2034,7 +2040,7 @@
       <c r="I50" s="19"/>
       <c r="J50" s="20"/>
     </row>
-    <row r="51" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B51" s="15" t="s">
         <v>8</v>
       </c>
@@ -2057,7 +2063,7 @@
       <c r="I51" s="19"/>
       <c r="J51" s="20"/>
     </row>
-    <row r="52" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B52" s="15" t="s">
         <v>8</v>
       </c>
@@ -2080,7 +2086,7 @@
       <c r="I52" s="19"/>
       <c r="J52" s="20"/>
     </row>
-    <row r="53" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B53" s="15" t="s">
         <v>8</v>
       </c>
@@ -2103,7 +2109,7 @@
       <c r="I53" s="19"/>
       <c r="J53" s="20"/>
     </row>
-    <row r="54" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B54" s="15" t="s">
         <v>8</v>
       </c>
@@ -2126,7 +2132,7 @@
       <c r="I54" s="19"/>
       <c r="J54" s="20"/>
     </row>
-    <row r="55" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B55" s="15" t="s">
         <v>8</v>
       </c>
@@ -2149,7 +2155,7 @@
       <c r="I55" s="19"/>
       <c r="J55" s="20"/>
     </row>
-    <row r="56" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B56" s="15" t="s">
         <v>8</v>
       </c>
@@ -2172,7 +2178,7 @@
       <c r="I56" s="19"/>
       <c r="J56" s="20"/>
     </row>
-    <row r="57" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B57" s="15" t="s">
         <v>8</v>
       </c>
@@ -2195,7 +2201,7 @@
       <c r="I57" s="19"/>
       <c r="J57" s="20"/>
     </row>
-    <row r="58" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B58" s="15" t="s">
         <v>8</v>
       </c>
@@ -2218,7 +2224,7 @@
       <c r="I58" s="19"/>
       <c r="J58" s="20"/>
     </row>
-    <row r="59" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B59" s="15" t="s">
         <v>8</v>
       </c>
@@ -2241,7 +2247,7 @@
       <c r="I59" s="19"/>
       <c r="J59" s="20"/>
     </row>
-    <row r="60" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B60" s="15" t="s">
         <v>8</v>
       </c>
@@ -2264,7 +2270,7 @@
       <c r="I60" s="19"/>
       <c r="J60" s="20"/>
     </row>
-    <row r="61" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B61" s="15" t="s">
         <v>8</v>
       </c>
@@ -2287,7 +2293,7 @@
       <c r="I61" s="19"/>
       <c r="J61" s="20"/>
     </row>
-    <row r="62" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B62" s="15" t="s">
         <v>8</v>
       </c>
@@ -2310,7 +2316,7 @@
       <c r="I62" s="19"/>
       <c r="J62" s="20"/>
     </row>
-    <row r="63" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B63" s="15" t="s">
         <v>8</v>
       </c>
@@ -2333,7 +2339,7 @@
       <c r="I63" s="19"/>
       <c r="J63" s="20"/>
     </row>
-    <row r="64" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B64" s="15" t="s">
         <v>8</v>
       </c>
@@ -2356,7 +2362,7 @@
       <c r="I64" s="19"/>
       <c r="J64" s="20"/>
     </row>
-    <row r="65" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B65" s="15" t="s">
         <v>8</v>
       </c>
@@ -2379,7 +2385,7 @@
       <c r="I65" s="19"/>
       <c r="J65" s="20"/>
     </row>
-    <row r="66" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B66" s="15" t="s">
         <v>8</v>
       </c>
@@ -2402,7 +2408,7 @@
       <c r="I66" s="19"/>
       <c r="J66" s="20"/>
     </row>
-    <row r="67" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B67" s="15" t="s">
         <v>8</v>
       </c>
@@ -2425,7 +2431,7 @@
       <c r="I67" s="19"/>
       <c r="J67" s="20"/>
     </row>
-    <row r="68" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B68" s="15" t="s">
         <v>8</v>
       </c>
@@ -2448,7 +2454,7 @@
       <c r="I68" s="19"/>
       <c r="J68" s="20"/>
     </row>
-    <row r="69" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B69" s="15" t="s">
         <v>8</v>
       </c>
@@ -2462,7 +2468,7 @@
         <v>64</v>
       </c>
       <c r="F69" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G69" s="18">
         <v>781242</v>
@@ -2471,7 +2477,7 @@
       <c r="I69" s="19"/>
       <c r="J69" s="20"/>
     </row>
-    <row r="70" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B70" s="15" t="s">
         <v>8</v>
       </c>
@@ -2485,7 +2491,7 @@
         <v>65</v>
       </c>
       <c r="F70" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G70" s="18">
         <v>781242</v>
@@ -2494,7 +2500,7 @@
       <c r="I70" s="19"/>
       <c r="J70" s="20"/>
     </row>
-    <row r="71" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B71" s="15" t="s">
         <v>8</v>
       </c>
@@ -2508,7 +2514,7 @@
         <v>66</v>
       </c>
       <c r="F71" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G71" s="18">
         <v>781242</v>
@@ -2517,7 +2523,7 @@
       <c r="I71" s="19"/>
       <c r="J71" s="20"/>
     </row>
-    <row r="72" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B72" s="15" t="s">
         <v>8</v>
       </c>
@@ -2531,7 +2537,7 @@
         <v>67</v>
       </c>
       <c r="F72" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G72" s="18">
         <v>781242</v>
@@ -2540,7 +2546,7 @@
       <c r="I72" s="19"/>
       <c r="J72" s="20"/>
     </row>
-    <row r="73" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B73" s="15" t="s">
         <v>8</v>
       </c>
@@ -2554,7 +2560,7 @@
         <v>68</v>
       </c>
       <c r="F73" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G73" s="18">
         <v>781242</v>
@@ -2563,7 +2569,7 @@
       <c r="I73" s="19"/>
       <c r="J73" s="20"/>
     </row>
-    <row r="74" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B74" s="15" t="s">
         <v>8</v>
       </c>
@@ -2577,7 +2583,7 @@
         <v>69</v>
       </c>
       <c r="F74" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G74" s="18">
         <v>781242</v>
@@ -2586,7 +2592,7 @@
       <c r="I74" s="19"/>
       <c r="J74" s="20"/>
     </row>
-    <row r="75" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B75" s="15" t="s">
         <v>8</v>
       </c>
@@ -2600,7 +2606,7 @@
         <v>70</v>
       </c>
       <c r="F75" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G75" s="18">
         <v>781242</v>
@@ -2609,7 +2615,7 @@
       <c r="I75" s="19"/>
       <c r="J75" s="20"/>
     </row>
-    <row r="76" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B76" s="15" t="s">
         <v>8</v>
       </c>
@@ -2623,7 +2629,7 @@
         <v>71</v>
       </c>
       <c r="F76" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G76" s="18">
         <v>781242</v>
@@ -2632,7 +2638,7 @@
       <c r="I76" s="19"/>
       <c r="J76" s="20"/>
     </row>
-    <row r="77" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B77" s="15" t="s">
         <v>8</v>
       </c>
@@ -2646,7 +2652,7 @@
         <v>72</v>
       </c>
       <c r="F77" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G77" s="18">
         <v>781242</v>
@@ -2655,7 +2661,7 @@
       <c r="I77" s="19"/>
       <c r="J77" s="20"/>
     </row>
-    <row r="78" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B78" s="15" t="s">
         <v>8</v>
       </c>
@@ -2669,7 +2675,7 @@
         <v>73</v>
       </c>
       <c r="F78" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G78" s="18">
         <v>781242</v>
@@ -2678,7 +2684,7 @@
       <c r="I78" s="19"/>
       <c r="J78" s="20"/>
     </row>
-    <row r="79" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B79" s="15" t="s">
         <v>8</v>
       </c>
@@ -2692,7 +2698,7 @@
         <v>74</v>
       </c>
       <c r="F79" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G79" s="18">
         <v>781242</v>
@@ -2701,7 +2707,7 @@
       <c r="I79" s="19"/>
       <c r="J79" s="20"/>
     </row>
-    <row r="80" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B80" s="15" t="s">
         <v>8</v>
       </c>
@@ -2715,7 +2721,7 @@
         <v>75</v>
       </c>
       <c r="F80" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G80" s="18">
         <v>781242</v>
@@ -2724,7 +2730,7 @@
       <c r="I80" s="19"/>
       <c r="J80" s="20"/>
     </row>
-    <row r="81" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="81" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B81" s="15" t="s">
         <v>8</v>
       </c>
@@ -2738,7 +2744,7 @@
         <v>76</v>
       </c>
       <c r="F81" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G81" s="18">
         <v>781242</v>
@@ -2747,7 +2753,7 @@
       <c r="I81" s="19"/>
       <c r="J81" s="20"/>
     </row>
-    <row r="82" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="82" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B82" s="15" t="s">
         <v>8</v>
       </c>
@@ -2761,7 +2767,7 @@
         <v>77</v>
       </c>
       <c r="F82" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G82" s="18">
         <v>781242</v>
@@ -2770,7 +2776,7 @@
       <c r="I82" s="19"/>
       <c r="J82" s="20"/>
     </row>
-    <row r="83" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="83" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B83" s="15" t="s">
         <v>8</v>
       </c>
@@ -2784,7 +2790,7 @@
         <v>78</v>
       </c>
       <c r="F83" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G83" s="18">
         <v>781242</v>
@@ -2793,7 +2799,7 @@
       <c r="I83" s="19"/>
       <c r="J83" s="20"/>
     </row>
-    <row r="84" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="84" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B84" s="15" t="s">
         <v>8</v>
       </c>
@@ -2807,7 +2813,7 @@
         <v>79</v>
       </c>
       <c r="F84" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G84" s="18">
         <v>781242</v>
@@ -2816,7 +2822,7 @@
       <c r="I84" s="19"/>
       <c r="J84" s="20"/>
     </row>
-    <row r="85" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="85" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B85" s="15" t="s">
         <v>8</v>
       </c>
@@ -2830,7 +2836,7 @@
         <v>80</v>
       </c>
       <c r="F85" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G85" s="18">
         <v>781242</v>
@@ -2839,7 +2845,7 @@
       <c r="I85" s="19"/>
       <c r="J85" s="20"/>
     </row>
-    <row r="86" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="86" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B86" s="15" t="s">
         <v>8</v>
       </c>
@@ -2853,7 +2859,7 @@
         <v>81</v>
       </c>
       <c r="F86" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G86" s="18">
         <v>781242</v>
@@ -2862,7 +2868,7 @@
       <c r="I86" s="19"/>
       <c r="J86" s="20"/>
     </row>
-    <row r="87" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="87" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B87" s="15" t="s">
         <v>8</v>
       </c>
@@ -2876,7 +2882,7 @@
         <v>82</v>
       </c>
       <c r="F87" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G87" s="18">
         <v>781242</v>
@@ -2885,7 +2891,7 @@
       <c r="I87" s="19"/>
       <c r="J87" s="20"/>
     </row>
-    <row r="88" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="88" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B88" s="15" t="s">
         <v>8</v>
       </c>
@@ -2899,7 +2905,7 @@
         <v>83</v>
       </c>
       <c r="F88" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G88" s="18">
         <v>781242</v>
@@ -2908,7 +2914,7 @@
       <c r="I88" s="19"/>
       <c r="J88" s="20"/>
     </row>
-    <row r="89" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="89" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B89" s="15" t="s">
         <v>8</v>
       </c>
@@ -2922,7 +2928,7 @@
         <v>84</v>
       </c>
       <c r="F89" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G89" s="18">
         <v>781242</v>
@@ -2931,7 +2937,7 @@
       <c r="I89" s="19"/>
       <c r="J89" s="20"/>
     </row>
-    <row r="90" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="90" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B90" s="15" t="s">
         <v>8</v>
       </c>
@@ -2945,7 +2951,7 @@
         <v>85</v>
       </c>
       <c r="F90" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G90" s="18">
         <v>781242</v>
@@ -2954,7 +2960,7 @@
       <c r="I90" s="19"/>
       <c r="J90" s="20"/>
     </row>
-    <row r="91" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="91" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B91" s="15" t="s">
         <v>8</v>
       </c>
@@ -2968,7 +2974,7 @@
         <v>86</v>
       </c>
       <c r="F91" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G91" s="18">
         <v>781242</v>
@@ -2977,7 +2983,7 @@
       <c r="I91" s="19"/>
       <c r="J91" s="20"/>
     </row>
-    <row r="92" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="92" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B92" s="15" t="s">
         <v>8</v>
       </c>
@@ -2991,7 +2997,7 @@
         <v>87</v>
       </c>
       <c r="F92" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G92" s="18">
         <v>781242</v>
@@ -3000,7 +3006,7 @@
       <c r="I92" s="19"/>
       <c r="J92" s="20"/>
     </row>
-    <row r="93" spans="2:10" x14ac:dyDescent="0.35">
+    <row r="93" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B93" s="15" t="s">
         <v>8</v>
       </c>
@@ -3014,7 +3020,7 @@
         <v>88</v>
       </c>
       <c r="F93" s="18">
-        <v>31249</v>
+        <v>27578</v>
       </c>
       <c r="G93" s="18">
         <v>781242</v>
@@ -3023,57 +3029,80 @@
       <c r="I93" s="19"/>
       <c r="J93" s="20"/>
     </row>
-    <row r="94" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B94" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="C94" s="22" t="s">
-        <v>9</v>
-      </c>
-      <c r="D94" s="23" t="s">
-        <v>10</v>
-      </c>
-      <c r="E94" s="22" t="s">
+    <row r="94" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B94" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="C94" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="D94" s="17" t="s">
+        <v>10</v>
+      </c>
+      <c r="E94" s="16" t="s">
         <v>89</v>
       </c>
-      <c r="F94" s="24">
-        <v>26041</v>
-      </c>
-      <c r="G94" s="24">
-        <v>781242</v>
-      </c>
-      <c r="H94" s="25"/>
-      <c r="I94" s="25"/>
-      <c r="J94" s="26"/>
-    </row>
-    <row r="99" spans="2:10" x14ac:dyDescent="0.35">
-      <c r="B99" s="32" t="s">
-        <v>99</v>
-      </c>
-      <c r="C99" s="32"/>
-      <c r="H99" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="I99" s="1"/>
-      <c r="J99" s="1"/>
-    </row>
-    <row r="100" spans="2:10" x14ac:dyDescent="0.35">
+      <c r="F94" s="18">
+        <v>27578</v>
+      </c>
+      <c r="G94" s="18">
+        <v>781242</v>
+      </c>
+      <c r="H94" s="19"/>
+      <c r="I94" s="19"/>
+      <c r="J94" s="20"/>
+    </row>
+    <row r="95" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B95" s="21" t="s">
+        <v>8</v>
+      </c>
+      <c r="C95" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="D95" s="23" t="s">
+        <v>91</v>
+      </c>
+      <c r="E95" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="F95" s="24">
+        <v>29600</v>
+      </c>
+      <c r="G95" s="24">
+        <v>828116</v>
+      </c>
+      <c r="H95" s="25"/>
+      <c r="I95" s="25"/>
+      <c r="J95" s="26"/>
+    </row>
+    <row r="100" spans="2:10" x14ac:dyDescent="0.25">
       <c r="B100" s="32" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="C100" s="32"/>
       <c r="H100" s="1" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="I100" s="1"/>
       <c r="J100" s="1"/>
     </row>
+    <row r="101" spans="2:10" x14ac:dyDescent="0.25">
+      <c r="B101" s="32" t="s">
+        <v>100</v>
+      </c>
+      <c r="C101" s="32"/>
+      <c r="H101" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="I101" s="1"/>
+      <c r="J101" s="1"/>
+    </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="B101:C101"/>
     <mergeCell ref="B100:C100"/>
-    <mergeCell ref="B99:C99"/>
+    <mergeCell ref="H101:J101"/>
     <mergeCell ref="H100:J100"/>
-    <mergeCell ref="H99:J99"/>
     <mergeCell ref="B11:D11"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="D2:J5"/>
